--- a/output/sql_management_summary.xlsx
+++ b/output/sql_management_summary.xlsx
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,7 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+      <color rgb="00595959"/>
       <sz val="11"/>
     </font>
     <font>
@@ -54,12 +55,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F497D"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F497D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -68,17 +63,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -95,12 +81,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F497D"/>
         <bgColor rgb="001F497D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,26 +110,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,96 +486,250 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE RISK ANALYTICS REPORT</t>
+          <t>DATA WAREHOUSE RISK ANALYTICS SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source Engine: SQLite Relational Matrix | Mode: Automated</t>
+          <t>Source: SQLite Relational Warehouse (reconciliation_matrix)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>AGGREGATED CAPITAL AT RISK</t>
+          <t>TOTAL EXCEPTIONS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TOTAL AUDIT BREACHES</t>
+          <t>TOTAL CAPITAL AT RISK ($)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>51500</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>SYSTEMIC CONCENTRATION ANALYSIS (BY TICKER)</t>
-        </is>
+        <v>1361714.799999992</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Ticker Symbol</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Total Outstanding Incidents</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Concentrated Risk Value Exposure</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>EXCEPTION CONCENTRATION BY TYPE</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>MEL_AIRPORT</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>50000</v>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Exception Type</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Incidents</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Risk Value ($)</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
+          <t>UNLISTED_VALUATION_LAG</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>562777.8999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>COUPON_TIMING_LAG</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>1500</v>
+      <c r="C11" s="9" t="n">
+        <v>462867.2899999917</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>QUANTITY_BREAK</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>143013.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>PRICING_BREAK</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>107858.8399999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>CASH_BALANCE_BREAK</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>FX_VALUATION_BREAK</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>18399.00000000023</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>CA_DRP_TIMING_LAG</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>18297.89999999991</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>EXCEPTION CONCENTRATION BY ASSET CLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Incidents</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Risk Value ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Unlisted/Alternatives</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>562777.8999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>462867.2899999917</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>AU Equities</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>161311.7699999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>US Equities</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>126257.8400000002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>48500</v>
       </c>
     </row>
   </sheetData>
